--- a/onderzoek_meta_alle_machines.xlsx
+++ b/onderzoek_meta_alle_machines.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,200 +487,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>318.5</v>
+        <v>18.59259259259252</v>
       </c>
       <c r="F2" t="n">
-        <v>318.5</v>
+        <v>18.59259259259252</v>
       </c>
       <c r="G2" t="n">
-        <v>42.31884799999898</v>
+        <v>3.501403799999025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01914030000079947</v>
+        <v>0.01797349999833386</v>
       </c>
       <c r="I2" t="n">
-        <v>42.33798829999978</v>
+        <v>3.519377299997359</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>202.7619047619045</v>
-      </c>
-      <c r="F3" t="n">
-        <v>202.7619047619045</v>
-      </c>
-      <c r="G3" t="n">
-        <v>40.04274620000069</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.02091260000088369</v>
-      </c>
-      <c r="I3" t="n">
-        <v>40.06365880000158</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36.33849144053233</v>
-      </c>
-      <c r="K3" t="n">
-        <v>36.33849144053233</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>94.01010101010088</v>
-      </c>
-      <c r="F4" t="n">
-        <v>94.01010101010088</v>
-      </c>
-      <c r="G4" t="n">
-        <v>40.7074864999995</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.01973039999938919</v>
-      </c>
-      <c r="I4" t="n">
-        <v>40.72721689999889</v>
-      </c>
-      <c r="J4" t="n">
-        <v>70.48348476919909</v>
-      </c>
-      <c r="K4" t="n">
-        <v>70.48348476919909</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>92.34782608695656</v>
-      </c>
-      <c r="F5" t="n">
-        <v>92.34782608695656</v>
-      </c>
-      <c r="G5" t="n">
-        <v>41.36406360000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02221380000082718</v>
-      </c>
-      <c r="I5" t="n">
-        <v>41.38627740000084</v>
-      </c>
-      <c r="J5" t="n">
-        <v>71.00539212340453</v>
-      </c>
-      <c r="K5" t="n">
-        <v>71.00539212340453</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" t="n">
-        <v>21.50000000000008</v>
-      </c>
-      <c r="F6" t="n">
-        <v>21.50000000000008</v>
-      </c>
-      <c r="G6" t="n">
-        <v>43.42193170000064</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02185079999981099</v>
-      </c>
-      <c r="I6" t="n">
-        <v>43.44378250000045</v>
-      </c>
-      <c r="J6" t="n">
-        <v>93.2496075353218</v>
-      </c>
-      <c r="K6" t="n">
-        <v>93.2496075353218</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B7" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" t="n">
-        <v>25</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.799999999999994</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.799999999999994</v>
-      </c>
-      <c r="G7" t="n">
-        <v>40.14507129999947</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02002429999993183</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40.1650955999994</v>
-      </c>
-      <c r="J7" t="n">
-        <v>99.43485086342228</v>
-      </c>
-      <c r="K7" t="n">
-        <v>99.43485086342228</v>
       </c>
     </row>
   </sheetData>

--- a/onderzoek_meta_alle_machines.xlsx
+++ b/onderzoek_meta_alle_machines.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,37 +475,212 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>18.59259259259252</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>18.59259259259252</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.501403799999025</v>
+        <v>35.44137240000055</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01797349999833386</v>
+        <v>0.0184835000000021</v>
       </c>
       <c r="I2" t="n">
-        <v>3.519377299997359</v>
+        <v>35.45985590000055</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.326278659611972</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.326278659611972</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35.27929769999901</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01794929999960004</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35.29724699999861</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-38.77131099353288</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-38.77131099353288</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.268591426071751</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.268591426071751</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.46049299999868</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.01831209999727434</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35.47880509999595</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-54.47652376786252</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-54.47652376786252</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35.57480009999927</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.57480009999927</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35.47212800000125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.47212800000125</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35.9180137000003</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.9180137000003</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
